--- a/Output/Ahamove/04. OPS_METRICS/2026-07-lh-logic-review-explained.xlsx
+++ b/Output/Ahamove/04. OPS_METRICS/2026-07-lh-logic-review-explained.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Tổng Quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. FM Offload — 7 Bước" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SOC Offload — 10 Bước" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. offload_fault &amp; FIFO" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Loại Trừ &amp; Return" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. Source Mapping" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Tổng Quan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. FM Offload — 7 Bước" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SOC Offload — 10 Bước" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. offload_fault &amp; FIFO" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Loại Trừ &amp; Return" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +71,25 @@
       <color rgb="001E293B"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -150,8 +168,14 @@
         <bgColor rgb="00D6E4F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F9FA"/>
+        <bgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -217,11 +241,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -281,6 +319,24 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,6 +703,279 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>BẢN ĐỒ ĐỐI SOÁT DỮ LIỆU NGUỒN (DATA SOURCE MAPPING)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Sheet trong File Explained</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Mục / Section Nội dung</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>File Nguồn Tương ứng (Source File)</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>Sheet &amp; Dòng/Cột Nguồn (Source Location)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>1. Tổng Quan</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Tổng quan Luồng KPI &amp; Sơ đồ Workflow</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>Review workflow LH offload KPI.xlsx</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>Sheet Info &amp; Sheet Code review (Dòng 1-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>2. FM Offload COT</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Logic 7 Bước FM Offload &amp; Công thức SLA End</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>Sheet FM_offload (Dòng 1 – 81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Mục 1 – 6: Nguồn Data, Cleanse &amp; 3TH Mapping COT</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 1 – 77, Cột A-M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Mục 7: Phân Lỗi offload_fault (SOC vs Linehaul Fault)</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 80 – 95, Cột N, O, P &amp; Cột A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Mục 8: Cơ chế &amp; Thuật toán FIFO (lh_adhoc_soc_miss_fifo)</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 130 – 178, Cột A-P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Mục 9: Logic KPI Month &amp; Bộ lọc WHERE</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 181 – 190, Cột A-E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Mục 10: 4 Quy tắc Loại trừ Cuối khỏi KPI</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 191 – 203, Cột A-E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Mục 11: Bảng Mapping Lý do Vận hành (explain_reason)</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 204 – 213, Cột A-E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>4. KPI Month &amp; Status</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>Bảng Status Code FMS &amp; Normalize Tên Station</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Review workflow LH offload KPI.xlsx</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>Sheet Code review &amp; Sheet Liên quan đến phân loại station</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>5. Glossary</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Định nghĩa chuẩn hóa thuật ngữ Vận hành</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Tổng hợp từ cả 2 File Source</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Tất cả các Sheet trong 2 file nguồn</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1041,7 +1370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1227,9 +1556,9 @@
 • depart_code: HNI satellite → '20-HNI'; Seller/SPC → regex; còn lại → prefix XX-YYY</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
@@ -1453,9 +1782,9 @@
           <t>⚠️ fm_cot không còn dùng chính (SPBIOVNS-24055). Status FM theo ticket được ưu tiên.</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="7" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="B34" s="5" t="inlineStr">
@@ -1689,15 +2018,15 @@
           <t>Loại trừ: a) fm_miss_fifo — vi phạm FIFO  |  b) gsheet_offload_remove — LH input thủ công</t>
         </is>
       </c>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B26:E26"/>
     <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B26:E26"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B13:E13"/>
@@ -1711,7 +2040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1761,9 +2090,9 @@
 Ngày thường: dùng start_time và eta_time gốc</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="7" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
@@ -1782,9 +2111,9 @@
 buyer_city: nếu city có trong COT → giữ nguyên; ngược lại → 'ALL' (fallback toàn tỉnh)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
@@ -2059,9 +2388,9 @@
           <t>Dùng trong Adhoc Extend: ticket được duyệt → cho phép trễ tối đa 1/2/3 COT tiếp theo</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
@@ -2160,9 +2489,9 @@
 buyer_city  = COALESCE(hub_zone.old_ct, fact.buyr_ct)</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="7" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="B41" s="5" t="inlineStr">
@@ -2249,9 +2578,9 @@
         sla_eta_offload   = MIN(COALESCE(TH3.eta,   TH2.eta,   TH1.eta))</t>
         </is>
       </c>
-      <c r="C46" s="24" t="n"/>
-      <c r="D46" s="24" t="n"/>
-      <c r="E46" s="24" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="7" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="B48" s="5" t="inlineStr">
@@ -2547,9 +2876,9 @@
 Loại trừ thêm: hub_hold_hang | soc_miss_fifo | remove_portal | gsheet_offload_remove</t>
         </is>
       </c>
-      <c r="C69" s="20" t="n"/>
-      <c r="D69" s="20" t="n"/>
-      <c r="E69" s="20" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2559,7 +2888,6 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B69:E69"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B38:E38"/>
@@ -2567,6 +2895,7 @@
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B32:E32"/>
@@ -2575,7 +2904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2983,9 +3312,9 @@
   cot_lh  = sla_eta_offload - 6 phút      cot_soc = sla_lhpacked_eta_ontime - 6 phút</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
@@ -3050,9 +3379,9 @@
 → row_number() OVER (PARTITION BY ngày,station,cot_lh,cot_soc ORDER BY soc_received) để chọn N đơn đầu</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="20" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3067,7 +3396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3371,9 +3700,9 @@
 Sau:   đã có log Return_SOC_LHPacked → ưu tiên LHPacked, fallback về Return_SOC_Returned</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Output/Ahamove/04. OPS_METRICS/2026-07-lh-logic-review-explained.xlsx
+++ b/Output/Ahamove/04. OPS_METRICS/2026-07-lh-logic-review-explained.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +86,13 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00FF7F32"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -259,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -338,6 +345,7 @@
     <xf numFmtId="0" fontId="10" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -703,12 +711,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E14"/>
+  <dimension ref="B2:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
@@ -716,19 +724,19 @@
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="26" t="inlineStr">
         <is>
-          <t>BẢN ĐỒ ĐỐI SOÁT DỮ LIỆU NGUỒN (DATA SOURCE MAPPING)</t>
+          <t>BẢN ĐỒ ĐỐI SOÁT DỮ LIỆU NGUỒN (LOGIC REVIEW EXPLAINED)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>Sheet trong File Explained</t>
+          <t>Sheet trong File Logic Review</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>Mục / Section Nội dung</t>
+          <t>Nội dung Diễn giải Chi tiết</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
@@ -738,7 +746,7 @@
       </c>
       <c r="E4" s="27" t="inlineStr">
         <is>
-          <t>Sheet &amp; Dòng/Cột Nguồn (Source Location)</t>
+          <t>Sheet &amp; Dòng/Cột Nguồn Tương ứng</t>
         </is>
       </c>
     </row>
@@ -750,29 +758,29 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>Tổng quan Luồng KPI &amp; Sơ đồ Workflow</t>
+          <t>Tổng quan 7 Bước FM Offload &amp; 10 Bước SOC Offload</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>Review workflow LH offload KPI.xlsx</t>
+          <t>LH logic review (1) (1).xlsx &amp; Review workflow</t>
         </is>
       </c>
       <c r="E5" s="29" t="inlineStr">
         <is>
-          <t>Sheet Info &amp; Sheet Code review (Dòng 1-3)</t>
+          <t>Sheet FM_offload, SOC_offload &amp; Sheet Info</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>2. FM Offload COT</t>
+          <t>2. FM Offload — 7 Bước</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>Logic 7 Bước FM Offload &amp; Công thức SLA End</t>
+          <t>Chi tiết 7 bước FM: Inbound info, status 8/400/42, actual_start &amp; SLA End</t>
         </is>
       </c>
       <c r="D6" s="31" t="inlineStr">
@@ -789,12 +797,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>3. SOC Offload COT</t>
+          <t>3. SOC Offload — 10 Bước</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>Mục 1 – 6: Nguồn Data, Cleanse &amp; 3TH Mapping COT</t>
+          <t>Chi tiết 10 bước SOC: Raw status, cot_exclude, dedup, Extend holiday, 3TH COT, phán định &amp; KPI Month</t>
         </is>
       </c>
       <c r="D7" s="29" t="inlineStr">
@@ -804,19 +812,19 @@
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>Sheet SOC_offload (Dòng 1 – 77, Cột A-M)</t>
+          <t>Sheet SOC_offload (Dòng 1 – 213, Cột A-M)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>3. SOC Offload COT</t>
+          <t>4. offload_fault &amp; FIFO</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>Mục 7: Phân Lỗi offload_fault (SOC vs Linehaul Fault)</t>
+          <t>1. Ma trận phán định offload_fault (11 quy tắc phân lỗi SOC vs Linehaul)</t>
         </is>
       </c>
       <c r="D8" s="31" t="inlineStr">
@@ -826,19 +834,19 @@
       </c>
       <c r="E8" s="31" t="inlineStr">
         <is>
-          <t>Sheet SOC_offload (Dòng 80 – 95, Cột N, O, P &amp; Cột A)</t>
+          <t>Sheet SOC_offload (Dòng 80 – 95, Cột N, O, P và Cột A)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>3. SOC Offload COT</t>
+          <t>4. offload_fault &amp; FIFO</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>Mục 8: Cơ chế &amp; Thuật toán FIFO (lh_adhoc_soc_miss_fifo)</t>
+          <t>2. Diễn giải Nhãn hiển thị Dashboard (explain_reason)</t>
         </is>
       </c>
       <c r="D9" s="29" t="inlineStr">
@@ -848,19 +856,19 @@
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>Sheet SOC_offload (Dòng 130 – 178, Cột A-P)</t>
+          <t>Sheet SOC_offload (Dòng 204 – 213, Cột A-E)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>3. SOC Offload COT</t>
+          <t>4. offload_fault &amp; FIFO</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Mục 9: Logic KPI Month &amp; Bộ lọc WHERE</t>
+          <t>3. Cơ chế &amp; Thuật toán phát hiện vi phạm FIFO (lh_adhoc_soc_miss_fifo)</t>
         </is>
       </c>
       <c r="D10" s="31" t="inlineStr">
@@ -870,19 +878,19 @@
       </c>
       <c r="E10" s="31" t="inlineStr">
         <is>
-          <t>Sheet SOC_offload (Dòng 181 – 190, Cột A-E)</t>
+          <t>Sheet SOC_offload (Dòng 130 – 178, Cột A-P)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>3. SOC Offload COT</t>
+          <t>5. Loại Trừ &amp; Return</t>
         </is>
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>Mục 10: 4 Quy tắc Loại trừ Cuối khỏi KPI</t>
+          <t>1. 4 Nguồn loại trừ cuối (hub_hold_hang, soc_miss_fifo, remove_portal, gsheet_offload_remove)</t>
         </is>
       </c>
       <c r="D11" s="29" t="inlineStr">
@@ -899,12 +907,12 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>3. SOC Offload COT</t>
+          <t>5. Loại Trừ &amp; Return</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Mục 11: Bảng Mapping Lý do Vận hành (explain_reason)</t>
+          <t>2. Logic actual_end đặc thù cho đơn Return &amp; Revert (Bulky, TO Transit, WH, CB, 4PL)</t>
         </is>
       </c>
       <c r="D12" s="31" t="inlineStr">
@@ -914,51 +922,7 @@
       </c>
       <c r="E12" s="31" t="inlineStr">
         <is>
-          <t>Sheet SOC_offload (Dòng 204 – 213, Cột A-E)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>4. KPI Month &amp; Status</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>Bảng Status Code FMS &amp; Normalize Tên Station</t>
-        </is>
-      </c>
-      <c r="D13" s="29" t="inlineStr">
-        <is>
-          <t>Review workflow LH offload KPI.xlsx</t>
-        </is>
-      </c>
-      <c r="E13" s="29" t="inlineStr">
-        <is>
-          <t>Sheet Code review &amp; Sheet Liên quan đến phân loại station</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>5. Glossary</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>Định nghĩa chuẩn hóa thuật ngữ Vận hành</t>
-        </is>
-      </c>
-      <c r="D14" s="31" t="inlineStr">
-        <is>
-          <t>Tổng hợp từ cả 2 File Source</t>
-        </is>
-      </c>
-      <c r="E14" s="31" t="inlineStr">
-        <is>
-          <t>Tất cả các Sheet trong 2 file nguồn</t>
+          <t>Sheet đơn return_revert (Dòng 1 – 17)</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1352,11 @@
   <sheetData>
     <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="32" t="inlineStr">
+        <is>
+          <t>📌 File Nguồn: Data sources/LH logic review (1) (1).xlsx [Sheet: FM_offload, Dòng 1-81]</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
@@ -2058,7 +2026,11 @@
   <sheetData>
     <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="32" t="inlineStr">
+        <is>
+          <t>📌 File Nguồn: Data sources/LH logic review (1) (1).xlsx [Sheet: SOC_offload, Dòng 1-213, Cột A-M]</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
@@ -2922,7 +2894,11 @@
   <sheetData>
     <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="32" t="inlineStr">
+        <is>
+          <t>📌 File Nguồn: Data sources/LH logic review (1) (1).xlsx [Sheet: SOC_offload, Dòng 80-95 (Cột N,O,P) &amp; Dòng 130-178]</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
@@ -3414,7 +3390,11 @@
   <sheetData>
     <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="32" t="inlineStr">
+        <is>
+          <t>📌 File Nguồn: Data sources/LH logic review (1) (1).xlsx [Sheet: đơn return_revert (Dòng 1-17) &amp; Sheet SOC_offload (Dòng 191-203)]</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
